--- a/InputData/trans/MPoEFUbVT/Max Perc of Each Fuel Usable by Veh Tech.xlsx
+++ b/InputData/trans/MPoEFUbVT/Max Perc of Each Fuel Usable by Veh Tech.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\trans\MPoEFUbVT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\MPoEFUbVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1ED3B24-060A-4F27-9B15-DA00296CC250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FBF57E-9E0A-4861-96FF-003F2EEA3BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1440" windowWidth="8870" windowHeight="7455" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="74">
   <si>
     <t>Sources:</t>
   </si>
@@ -365,9 +365,6 @@
   <si>
     <t>We use a 100% maximum value to represent drop-in biofuel replacements.</t>
   </si>
-  <si>
-    <t>Louisiana</t>
-  </si>
 </sst>
 </file>
 
@@ -501,7 +498,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -517,7 +514,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -830,24 +826,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C72"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B72"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="69.26953125" customWidth="1"/>
+    <col min="2" max="2" width="69.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45450</v>
-      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -855,285 +845,285 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2017</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" s="7">
         <v>44317</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <v>2016</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>66</v>
       </c>
@@ -1153,12 +1143,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -1268,7 +1258,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1378,7 +1368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1488,7 +1478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1598,7 +1588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1708,7 +1698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1818,7 +1808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1928,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2038,7 +2028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -2148,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -2258,7 +2248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -2379,7 +2369,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2391,12 +2381,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -2506,7 +2496,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2616,7 +2606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2726,7 +2716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2836,7 +2826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2946,7 +2936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -3056,7 +3046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -3166,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3276,7 +3266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -3386,7 +3376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -3496,7 +3486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -3617,12 +3607,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -3732,7 +3722,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3842,7 +3832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3952,7 +3942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4062,7 +4052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -4172,7 +4162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -4282,7 +4272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -4392,7 +4382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4502,7 +4492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -4612,7 +4602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -4722,7 +4712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -4843,12 +4833,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -4958,7 +4948,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -5068,7 +5058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5178,7 +5168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -5288,7 +5278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -5398,7 +5388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -5543,7 +5533,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -5653,7 +5643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5763,7 +5753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -5873,7 +5863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -5983,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -6104,12 +6094,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -6219,7 +6209,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6329,7 +6319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -6439,7 +6429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -6549,7 +6539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -6659,7 +6649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -6769,7 +6759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6914,7 +6904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -7024,7 +7014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -7134,7 +7124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -7244,7 +7234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -7365,12 +7355,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -7480,7 +7470,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -7590,7 +7580,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -7700,7 +7690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -7810,7 +7800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -7920,7 +7910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -8065,7 +8055,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -8175,7 +8165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -8285,7 +8275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -8395,7 +8385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -8505,7 +8495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -8626,12 +8616,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -8741,7 +8731,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -8851,7 +8841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -8961,7 +8951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -9071,7 +9061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -9181,7 +9171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -9291,7 +9281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -9401,7 +9391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -9511,7 +9501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -9621,7 +9611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -9731,7 +9721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -9852,12 +9842,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -9967,7 +9957,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -10077,7 +10067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -10187,7 +10177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -10297,7 +10287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -10407,7 +10397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -10517,7 +10507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -10627,7 +10617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -10737,7 +10727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -10847,7 +10837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -10957,7 +10947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -11078,7 +11068,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11087,17 +11077,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AI25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.40625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.15</v>
       </c>
@@ -11105,7 +11095,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -11113,12 +11103,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -11126,7 +11116,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0</v>
       </c>
@@ -11134,12 +11124,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2020</v>
       </c>
@@ -11147,7 +11137,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0</v>
       </c>
@@ -11155,12 +11145,12 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2016</v>
       </c>
@@ -11267,7 +11257,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0</v>
       </c>
@@ -11403,11 +11393,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2016</v>
       </c>
@@ -11514,7 +11504,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
@@ -11650,17 +11640,17 @@
         <v>0.59999999999999432</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
     </row>
@@ -11676,12 +11666,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -11791,7 +11781,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -11901,7 +11891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -12011,7 +12001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -12121,7 +12111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -12231,7 +12221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -12341,7 +12331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -12451,7 +12441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -12561,7 +12551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -12671,7 +12661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -12781,7 +12771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -12902,12 +12892,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -13017,7 +13007,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -13127,7 +13117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -13237,7 +13227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -13347,7 +13337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -13457,7 +13447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -13567,7 +13557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -13677,7 +13667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -13787,7 +13777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -13897,7 +13887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -14007,7 +13997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -14128,12 +14118,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -14243,7 +14233,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -14353,7 +14343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -14463,7 +14453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -14573,7 +14563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -14683,7 +14673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -14828,7 +14818,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -14938,7 +14928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -15048,7 +15038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -15158,7 +15148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -15268,7 +15258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -15389,12 +15379,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -15504,7 +15494,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -15614,7 +15604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -15724,7 +15714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15834,7 +15824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -15944,7 +15934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -16054,7 +16044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -16199,7 +16189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -16309,7 +16299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -16419,7 +16409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -16529,7 +16519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -16650,12 +16640,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -16765,7 +16755,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -16875,7 +16865,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -16985,7 +16975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -17095,7 +17085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -17205,7 +17195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -17315,7 +17305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -17460,7 +17450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -17570,7 +17560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -17680,7 +17670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -17790,7 +17780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -17911,12 +17901,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -18026,7 +18016,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -18136,7 +18126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -18246,7 +18236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -18356,7 +18346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -18466,7 +18456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -18576,7 +18566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -18686,7 +18676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -18796,7 +18786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -18906,7 +18896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -19016,7 +19006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -19137,12 +19127,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -19252,7 +19242,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -19362,7 +19352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -19472,7 +19462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -19582,7 +19572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -19692,7 +19682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -19802,7 +19792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -19912,7 +19902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -20022,7 +20012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -20132,7 +20122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -20242,7 +20232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -20363,7 +20353,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20375,12 +20365,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -20490,7 +20480,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -20600,7 +20590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -20710,7 +20700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -20820,7 +20810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -20930,7 +20920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -21040,7 +21030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -21150,7 +21140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -21260,7 +21250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -21370,7 +21360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -21480,7 +21470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -21601,12 +21591,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -21716,7 +21706,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -21826,7 +21816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -21936,7 +21926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -22046,7 +22036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -22156,7 +22146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -22266,7 +22256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -22376,7 +22366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -22486,7 +22476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -22596,7 +22586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -22706,7 +22696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -22827,7 +22817,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22839,12 +22829,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -22954,7 +22944,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -23064,7 +23054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -23174,7 +23164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -23284,7 +23274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -23394,7 +23384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -23539,7 +23529,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -23649,7 +23639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -23759,7 +23749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -23869,7 +23859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -23979,7 +23969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -24100,12 +24090,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -24215,7 +24205,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -24325,7 +24315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -24435,7 +24425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -24545,7 +24535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -24655,7 +24645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -24765,7 +24755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -24910,7 +24900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -25020,7 +25010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -25130,7 +25120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -25240,7 +25230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -25361,12 +25351,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -25476,7 +25466,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -25586,7 +25576,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -25696,7 +25686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -25806,7 +25796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -25916,7 +25906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -26026,7 +26016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -26171,7 +26161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -26281,7 +26271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -26391,7 +26381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -26501,7 +26491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -26622,12 +26612,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -26737,7 +26727,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -26847,7 +26837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -26957,7 +26947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -27067,7 +27057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -27177,7 +27167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -27287,7 +27277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -27397,7 +27387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -27507,7 +27497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -27617,7 +27607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -27727,7 +27717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -27848,12 +27838,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -27963,7 +27953,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -28073,7 +28063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -28183,7 +28173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -28293,7 +28283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -28403,7 +28393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -28513,7 +28503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -28623,7 +28613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -28733,7 +28723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -28843,7 +28833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -28953,7 +28943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -29074,7 +29064,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29086,12 +29076,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -29198,7 +29188,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -29305,7 +29295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -29412,7 +29402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -29519,7 +29509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -29626,7 +29616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -29733,7 +29723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -29840,7 +29830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -29947,7 +29937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -30054,7 +30044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -30161,7 +30151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -30279,12 +30269,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -30391,7 +30381,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -30498,7 +30488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -30605,7 +30595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -30712,7 +30702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -30819,7 +30809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -30926,7 +30916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -31033,7 +31023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -31140,7 +31130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -31247,7 +31237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -31354,7 +31344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -31472,12 +31462,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -31584,7 +31574,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -31691,7 +31681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -31798,7 +31788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -31905,7 +31895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -32012,7 +32002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -32153,7 +32143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -32260,7 +32250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -32367,7 +32357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -32474,7 +32464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -32581,7 +32571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -32699,12 +32689,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -32811,7 +32801,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -32918,7 +32908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -33025,7 +33015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -33132,7 +33122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -33239,7 +33229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -33346,7 +33336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -33487,7 +33477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -33594,7 +33584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -33701,7 +33691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -33808,7 +33798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -33926,12 +33916,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.26953125" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -34041,7 +34031,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -34151,7 +34141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -34261,7 +34251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -34371,7 +34361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -34481,7 +34471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -34591,7 +34581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -34701,7 +34691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -34811,7 +34801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -34921,7 +34911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -35031,7 +35021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -35152,12 +35142,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -35264,7 +35254,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -35371,7 +35361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -35478,7 +35468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -35585,7 +35575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -35692,7 +35682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -35799,7 +35789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -35906,7 +35896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -36013,7 +36003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -36120,7 +36110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -36227,7 +36217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -36345,7 +36335,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -36357,12 +36347,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -36469,7 +36459,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -36576,7 +36566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -36683,7 +36673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -36790,7 +36780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -36897,7 +36887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -37004,7 +36994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -37111,7 +37101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -37218,7 +37208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -37325,7 +37315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -37432,7 +37422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -37550,12 +37540,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -37662,7 +37652,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -37769,7 +37759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -37876,7 +37866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -37983,7 +37973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -38090,7 +38080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -38197,7 +38187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -38304,7 +38294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -38411,7 +38401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -38518,7 +38508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -38625,7 +38615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -38743,12 +38733,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -38855,7 +38845,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -38962,7 +38952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -39069,7 +39059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -39176,7 +39166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -39283,7 +39273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -39424,7 +39414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -39531,7 +39521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -39638,7 +39628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -39745,7 +39735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -39852,7 +39842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -39970,12 +39960,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -40082,7 +40072,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -40189,7 +40179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -40296,7 +40286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -40403,7 +40393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -40510,7 +40500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -40617,7 +40607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -40758,7 +40748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -40865,7 +40855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -40972,7 +40962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -41079,7 +41069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -41197,12 +41187,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -41309,7 +41299,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -41416,7 +41406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -41523,7 +41513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -41630,7 +41620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -41737,7 +41727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -41844,7 +41834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -41951,7 +41941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -42058,7 +42048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -42165,7 +42155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -42272,7 +42262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -42390,7 +42380,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -42402,12 +42392,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -42514,7 +42504,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -42621,7 +42611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -42728,7 +42718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -42835,7 +42825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -42942,7 +42932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -43049,7 +43039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -43156,7 +43146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -43263,7 +43253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -43370,7 +43360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -43477,7 +43467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -43595,12 +43585,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -43707,7 +43697,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -43814,7 +43804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -43921,7 +43911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -44028,7 +44018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -44135,7 +44125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -44242,7 +44232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -44349,7 +44339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -44456,7 +44446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -44563,7 +44553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -44670,7 +44660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -44788,12 +44778,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -44903,7 +44893,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -45013,7 +45003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -45123,7 +45113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -45233,7 +45223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -45343,7 +45333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -45453,7 +45443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -45563,7 +45553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -45673,7 +45663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -45783,7 +45773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -45893,7 +45883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -46014,12 +46004,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -46126,7 +46116,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -46233,7 +46223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -46340,7 +46330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -46447,7 +46437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -46554,7 +46544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -46695,7 +46685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -46802,7 +46792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -46909,7 +46899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -47016,7 +47006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -47123,7 +47113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -47241,12 +47231,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -47353,7 +47343,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -47460,7 +47450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -47567,7 +47557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -47674,7 +47664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -47781,7 +47771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -47888,7 +47878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -48029,7 +48019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -48136,7 +48126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -48243,7 +48233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -48350,7 +48340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -48468,12 +48458,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -48580,7 +48570,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -48687,7 +48677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -48794,7 +48784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -48901,7 +48891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -49008,7 +48998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -49115,7 +49105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -49222,7 +49212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -49329,7 +49319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -49436,7 +49426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -49543,7 +49533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -49661,7 +49651,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49673,12 +49663,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -49785,7 +49775,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -49892,7 +49882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -49999,7 +49989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -50106,7 +50096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -50213,7 +50203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -50320,7 +50310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -50427,7 +50417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -50534,7 +50524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -50641,7 +50631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -50748,7 +50738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -50866,12 +50856,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -50978,7 +50968,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -51085,7 +51075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -51192,7 +51182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -51299,7 +51289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -51406,7 +51396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -51513,7 +51503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -51620,7 +51610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -51727,7 +51717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -51834,7 +51824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -51941,7 +51931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -52059,12 +52049,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -52171,7 +52161,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -52278,7 +52268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -52385,7 +52375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -52492,7 +52482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -52599,7 +52589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -52740,7 +52730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -52847,7 +52837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -52954,7 +52944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -53061,7 +53051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -53168,7 +53158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -53286,12 +53276,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -53398,7 +53388,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -53505,7 +53495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -53612,7 +53602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -53719,7 +53709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -53826,7 +53816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -53933,7 +53923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -54074,7 +54064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -54181,7 +54171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -54288,7 +54278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -54395,7 +54385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -54513,12 +54503,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -54625,7 +54615,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -54732,7 +54722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -54839,7 +54829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -54946,7 +54936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -55053,7 +55043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -55160,7 +55150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -55267,7 +55257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -55374,7 +55364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -55481,7 +55471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -55588,7 +55578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -55706,7 +55696,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -55718,12 +55708,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -55833,7 +55823,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -55943,7 +55933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -56053,7 +56043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -56163,7 +56153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -56273,7 +56263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -56418,7 +56408,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -56528,7 +56518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -56638,7 +56628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -56748,7 +56738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -56858,7 +56848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -56979,12 +56969,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -57091,7 +57081,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -57198,7 +57188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -57305,7 +57295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -57412,7 +57402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -57519,7 +57509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -57626,7 +57616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -57733,7 +57723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -57840,7 +57830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -57947,7 +57937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -58054,7 +58044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -58172,12 +58162,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -58284,7 +58274,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -58391,7 +58381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -58498,7 +58488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -58605,7 +58595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -58712,7 +58702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -58819,7 +58809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -58926,7 +58916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -59033,7 +59023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -59140,7 +59130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -59247,7 +59237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -59365,12 +59355,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -59477,7 +59467,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -59584,7 +59574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -59691,7 +59681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -59798,7 +59788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -59905,7 +59895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -60046,7 +60036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -60153,7 +60143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -60260,7 +60250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -60367,7 +60357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -60474,7 +60464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -60592,12 +60582,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -60704,7 +60694,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -60811,7 +60801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -60918,7 +60908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -61025,7 +61015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -61132,7 +61122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -61239,7 +61229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -61380,7 +61370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -61487,7 +61477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -61594,7 +61584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -61701,7 +61691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -61819,12 +61809,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -61931,7 +61921,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -62038,7 +62028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -62145,7 +62135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -62252,7 +62242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -62359,7 +62349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -62466,7 +62456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -62573,7 +62563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -62680,7 +62670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -62787,7 +62777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -62894,7 +62884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -63012,7 +63002,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -63024,12 +63014,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -63136,7 +63126,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -63243,7 +63233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -63350,7 +63340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -63457,7 +63447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -63564,7 +63554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -63671,7 +63661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -63778,7 +63768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -63885,7 +63875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -63992,7 +63982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -64099,7 +64089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -64217,12 +64207,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -64329,7 +64319,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -64436,7 +64426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -64543,7 +64533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -64650,7 +64640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -64757,7 +64747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -64864,7 +64854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -64971,7 +64961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -65078,7 +65068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -65185,7 +65175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -65292,7 +65282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -65410,12 +65400,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -65522,7 +65512,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -65629,7 +65619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -65736,7 +65726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -65843,7 +65833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -65950,7 +65940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -66091,7 +66081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -66198,7 +66188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -66305,7 +66295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -66412,7 +66402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -66519,7 +66509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -66637,12 +66627,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -66749,7 +66739,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -66856,7 +66846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -66963,7 +66953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -67070,7 +67060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -67177,7 +67167,7 @@
         <v>0.42991564609237387</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -67284,7 +67274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -67425,7 +67415,7 @@
         <v>0.59999999999999432</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -67532,7 +67522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -67639,7 +67629,7 @@
         <v>0.57008435390762602</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -67746,7 +67736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -67864,12 +67854,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -67979,7 +67969,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -68089,7 +68079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -68199,7 +68189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -68309,7 +68299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -68419,7 +68409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -68529,7 +68519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -68639,7 +68629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -68749,7 +68739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -68859,7 +68849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -68969,7 +68959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -69090,12 +69080,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
@@ -69202,7 +69192,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -69309,7 +69299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -69416,7 +69406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -69523,7 +69513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -69630,7 +69620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -69737,7 +69727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -69844,7 +69834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -69951,7 +69941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -70058,7 +70048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -70165,7 +70155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -70283,7 +70273,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -70295,12 +70285,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -70410,7 +70400,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -70520,7 +70510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -70630,7 +70620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -70740,7 +70730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -70850,7 +70840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -70960,7 +70950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -71070,7 +71060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -71180,7 +71170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -71290,7 +71280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -71400,7 +71390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -71521,12 +71511,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -71636,7 +71626,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -71746,7 +71736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -71856,7 +71846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -71966,7 +71956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -72076,7 +72066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -72186,7 +72176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -72296,7 +72286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -72406,7 +72396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -72516,7 +72506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -72626,7 +72616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -72747,12 +72737,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -72862,7 +72852,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -72972,7 +72962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -73082,7 +73072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -73192,7 +73182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -73302,7 +73292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -73412,7 +73402,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -73522,7 +73512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -73632,7 +73622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -73742,7 +73732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -73852,7 +73842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -73973,12 +73963,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -74088,7 +74078,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -74198,7 +74188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -74308,7 +74298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -74418,7 +74408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -74528,7 +74518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -74638,7 +74628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -74748,7 +74738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -74858,7 +74848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -74968,7 +74958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -75078,7 +75068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -75199,12 +75189,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -75314,7 +75304,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -75424,7 +75414,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -75534,7 +75524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -75644,7 +75634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -75754,7 +75744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -75864,7 +75854,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -75974,7 +75964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -76084,7 +76074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -76194,7 +76184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -76304,7 +76294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -76425,12 +76415,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -76540,7 +76530,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -76650,7 +76640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -76760,7 +76750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -76870,7 +76860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -76980,7 +76970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -77090,7 +77080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -77200,7 +77190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -77310,7 +77300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -77420,7 +77410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -77530,7 +77520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -77651,12 +77641,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -77766,7 +77756,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -77876,7 +77866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -77986,7 +77976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -78096,7 +78086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -78206,7 +78196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -78316,7 +78306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -78426,7 +78416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -78536,7 +78526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -78646,7 +78636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -78756,7 +78746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -78877,7 +78867,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -78889,12 +78879,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -79004,7 +78994,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -79114,7 +79104,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -79224,7 +79214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -79334,7 +79324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -79444,7 +79434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -79589,7 +79579,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -79699,7 +79689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -79809,7 +79799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -79919,7 +79909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -80029,7 +80019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -80153,12 +80143,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -80268,7 +80258,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -80378,7 +80368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -80488,7 +80478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -80598,7 +80588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -80708,7 +80698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -80818,7 +80808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -80928,7 +80918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -81038,7 +81028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -81148,7 +81138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -81258,7 +81248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -81379,12 +81369,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -81494,7 +81484,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -81604,7 +81594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -81714,7 +81704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -81824,7 +81814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -81934,7 +81924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -82044,7 +82034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -82154,7 +82144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -82264,7 +82254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -82374,7 +82364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -82484,7 +82474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -82605,12 +82595,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -82720,7 +82710,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -82830,7 +82820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -82940,7 +82930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -83050,7 +83040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -83160,7 +83150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -83305,7 +83295,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -83415,7 +83405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -83525,7 +83515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -83635,7 +83625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -83745,7 +83735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -83866,12 +83856,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -83981,7 +83971,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -84091,7 +84081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -84201,7 +84191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -84311,7 +84301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -84421,7 +84411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -84531,7 +84521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -84676,7 +84666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -84786,7 +84776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -84896,7 +84886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -85006,7 +84996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -85127,12 +85117,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -85242,7 +85232,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -85352,7 +85342,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -85462,7 +85452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -85572,7 +85562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -85682,7 +85672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -85827,7 +85817,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -85937,7 +85927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -86047,7 +86037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -86157,7 +86147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -86267,7 +86257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -86388,12 +86378,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -86503,7 +86493,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -86613,7 +86603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -86723,7 +86713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -86833,7 +86823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -86943,7 +86933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -87053,7 +87043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -87163,7 +87153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -87273,7 +87263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -87383,7 +87373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -87493,7 +87483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -87614,12 +87604,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -87729,7 +87719,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -87839,7 +87829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -87949,7 +87939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -88059,7 +88049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -88169,7 +88159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -88279,7 +88269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -88389,7 +88379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -88499,7 +88489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -88609,7 +88599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -88719,7 +88709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -88840,12 +88830,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -88955,7 +88945,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -89065,7 +89055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -89175,7 +89165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -89285,7 +89275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -89395,7 +89385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -89505,7 +89495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -89615,7 +89605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -89725,7 +89715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -89835,7 +89825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -89945,7 +89935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
